--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T13:30:57+00:00</t>
+    <t>2023-04-28T11:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-28T11:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:34:44+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T04:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T04:59:44+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-01T18:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:23:44+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T17:19:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:40+00:00</t>
+    <t>2023-05-05T20:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:44:23+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
+++ b/ValueSet-vs-reason-for-assessment-or-test-not-performed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
